--- a/test-case-exports/BillManagement.xlsx
+++ b/test-case-exports/BillManagement.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="130">
   <si>
     <t>#</t>
   </si>
@@ -44,24 +44,183 @@
     <t>BillManagement</t>
   </si>
   <si>
+    <t>BusinessTestCases/BillManagement/functional/BillItems.spec.ts</t>
+  </si>
+  <si>
+    <t>Bill Items — At Least One Item Required (BI-01, BI-02)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>BI-01: creating a Detailed Bill after deleting every item should be blocked with a validation error (EMI-4069)</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>BI-02: editing a Detailed Bill down to zero items should be blocked with the same validation error (EMI-4179)</t>
+  </si>
+  <si>
+    <t>Skipped: No existing detailed bill available to edit — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>Bill Items — Calculation Correctness (BI-03, BI-04, BI-05, BI-06)</t>
+  </si>
+  <si>
+    <t>BI-03: an item with a Fixed discount should total (unitPrice - discount) x quantity (EMI-4123)</t>
+  </si>
+  <si>
+    <t>BI-04: /bills/calculate should return a correct netAmountAfterDiscount for FIXED-discount items (EMI-5030)</t>
+  </si>
+  <si>
+    <t>Skipped: /bills/calculate response was not JSON — check whether the payload is encrypted in this environment.</t>
+  </si>
+  <si>
+    <t>BI-05: editing an existing item should not make /bills/calculate return 500 (EMI-4071)</t>
+  </si>
+  <si>
+    <t>BI-26: characterizes which EMI-4121 discount interpretation is currently live (unit-price vs. line-total)</t>
+  </si>
+  <si>
+    <t>BI-06: a bill with more than two items should total the sum of every item, not a subset (EMI-2952)</t>
+  </si>
+  <si>
+    <t>Bill Items — Discount Behaviour (BI-07, BI-08, BI-09, BI-10, BI-11)</t>
+  </si>
+  <si>
+    <t>BI-07: editing an item discount should update the total bill amount immediately (EMI-3965)</t>
+  </si>
+  <si>
+    <t>BI-08: a Fixed item discount larger than the item amount should be flagged immediately under the amount field (EMI-3961)</t>
+  </si>
+  <si>
+    <t>BI-09: a bill-level Fixed discount larger than the bill total should be rejected (EMI-3323)</t>
+  </si>
+  <si>
+    <t>BI-10: reopening an item saved with "No Discount" should show "No Discount", not an empty field (EMI-3383)</t>
+  </si>
+  <si>
+    <t>BI-11: an item-level discount and a different bill-level discount type should coexist without corrupting the total (EMI-5319)</t>
+  </si>
+  <si>
+    <t>Bill Items — VAT Field (BI-12)</t>
+  </si>
+  <si>
+    <t>BI-12: VAT should stay optional when editing an item, exactly as it is when adding one (EMI-3957)</t>
+  </si>
+  <si>
+    <t>Bill Items — Deletion (BI-13, BI-14, BI-15, BI-16, BI-17)</t>
+  </si>
+  <si>
+    <t>BI-13: deleting the last remaining item should raise a confirmation dialog, and confirming should remove it (EMI-1988, EMI-2590)</t>
+  </si>
+  <si>
+    <t>BI-14: cancelling the last-item confirmation dialog should leave the item in place (EMI-1988)</t>
+  </si>
+  <si>
+    <t>BI-15: "Delete All" should actually empty the item list, not just show a success message (EMI-2100, EMI-1935)</t>
+  </si>
+  <si>
+    <t>BI-16: deleting an item should update the bill amount without raising an error (EMI-3282)</t>
+  </si>
+  <si>
+    <t>BI-17: removing an item should recalculate VAT and commission, not keep the removed item in the figures (EMI-2298)</t>
+  </si>
+  <si>
+    <t>Bill Items — Editing an Existing Bill (BI-18, BI-19, BI-20)</t>
+  </si>
+  <si>
+    <t>BI-18: adding an item while editing a bill should compute its total and preserve the existing items (EMI-3305)</t>
+  </si>
+  <si>
+    <t>BI-19: creating a Detailed Bill containing both a saved product and a manual item should succeed (EMI-3118)</t>
+  </si>
+  <si>
+    <t>BI-20: updating a Detailed Bill that contains both a product and an item should succeed (EMI-3119, EMI-1679)</t>
+  </si>
+  <si>
+    <t>Bill Items — Add Item Form Validation (BI-21, BI-22)</t>
+  </si>
+  <si>
+    <t>BI-21: leaving Discount Type and Discount empty should still allow the item to be added (EMI-1930)</t>
+  </si>
+  <si>
+    <t>BI-22: submitting the add-item form with every field empty should be rejected, not silently added (MJDPAY-775)</t>
+  </si>
+  <si>
+    <t>Bill Items — Edit-Bill Server Errors (BI-23, BI-24)</t>
+  </si>
+  <si>
+    <t>BI-23: adding an item in the Edit Item step and returning to Edit Bill should not return a 500 (EMI-1912)</t>
+  </si>
+  <si>
+    <t>BI-24: editing an existing item with a valid discount should not be blocked by discount validation (EMI-1709)</t>
+  </si>
+  <si>
+    <t>Bill Items — Product As Item (BI-25)</t>
+  </si>
+  <si>
+    <t>BI-25: picking a saved product in the create-bill step should add it as a priced line item (EMI-3060)</t>
+  </si>
+  <si>
+    <t>Bill Items — Get Bill By ID Response (BI-26)</t>
+  </si>
+  <si>
+    <t>BI-26: GET /bills/{id} should return the bill items, not an empty or unmapped list (EMI-4991)</t>
+  </si>
+  <si>
+    <t>Gated: No existing detailed bill available to open — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>BusinessTestCases/BillManagement/functional/BillsListPage.spec.ts</t>
+  </si>
+  <si>
+    <t>Bills Table — Page Loads Without Hanging (BLT-01, EMI-5616)</t>
+  </si>
+  <si>
+    <t>BLT-01: the My Bills page should finish loading rather than spin indefinitely</t>
+  </si>
+  <si>
+    <t>Bills Table — Pagination Advances Records (BLT-02, EMI-5807)</t>
+  </si>
+  <si>
+    <t>BLT-02: navigating to the next page should display a different set of records</t>
+  </si>
+  <si>
+    <t>Gated: No bills available to page through — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>Bills Table — Viewing an Owned Bill Is Authorized (BLT-03, EMI-5673)</t>
+  </si>
+  <si>
+    <t>BLT-03: opening a bill the biller owns should not return "could not be found, or you do not have the necessary permissions"</t>
+  </si>
+  <si>
+    <t>Skipped: No bills available to open — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>Bills Table — Expired Status Displayed (BLT-04, EMI-5119)</t>
+  </si>
+  <si>
+    <t>BLT-04: an expired bill should show an "Expired" status badge in the Bill Report</t>
+  </si>
+  <si>
+    <t>Gated: No expired bill present in the current data set to assert against — verify UAT data setup.</t>
+  </si>
+  <si>
     <t>BusinessTestCases/BillManagement/functional/CreateBillFlow.spec.ts</t>
   </si>
   <si>
     <t>Create Bill — Single Entry (CB-01, CB-02)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>CB-01: should create a bill with only the required fields</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>CB-02: should compute the amount breakdown correctly with VAT and a fixed discount</t>
   </si>
   <si>
@@ -113,24 +272,123 @@
     <t>CB-16: one invalid row in the batch should roll back the entire upload</t>
   </si>
   <si>
+    <t>Create Bill — Bulk Upload Edge Cases (CB-18, CB-19, CB-20, CB-21)</t>
+  </si>
+  <si>
+    <t>CB-18: uploading an Excel row with a MERCHANT payer type should not be rejected with INVALID_PAYER_TYPE</t>
+  </si>
+  <si>
+    <t>CB-19: uploading a valid Excel file and confirming should not fail with a 500 during bill generation</t>
+  </si>
+  <si>
+    <t>CB-20: an Excel bill reference containing letters should be accepted, not rejected with a 400 on upload</t>
+  </si>
+  <si>
+    <t>CB-21: an Excel row targeting an individual (national ID) payer should not fail with "The profile could not be found."</t>
+  </si>
+  <si>
+    <t>BusinessTestCases/BillManagement/functional/DetailedBillEditing.spec.ts</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — Editing an Existing Bill Succeeds (DBE-01, EMI-5809)</t>
+  </si>
+  <si>
+    <t>DBE-01: editing a Single or Detailed bill and submitting a change should succeed, not 400 Bad Request</t>
+  </si>
+  <si>
+    <t>Skipped: No existing bill available to edit — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — Discount Persists on Reopen (DBE-02, EMI-5893)</t>
+  </si>
+  <si>
+    <t>DBE-02: reopening a detailed bill for edit should show the previously applied discount, not "No Discount"</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — VAT Change Recalculates Summary Immediately (DBE-03, EMI-5812)</t>
+  </si>
+  <si>
+    <t>DBE-03: toggling VAT on a Detailed Bill should update VAT Amount and Grand Total without clicking Apply Discount</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — Discount Survives VAT Toggle (DBE-04, EMI-5863)</t>
+  </si>
+  <si>
+    <t>DBE-04: enabling/disabling VAT on a Detailed Bill should not clear an already-applied discount</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — Expired Bill Editing Allowed (DBE-05, EMI-5776)</t>
+  </si>
+  <si>
+    <t>DBE-05: editing an expired detailed bill should be allowed instead of failing with an unclear 400 error</t>
+  </si>
+  <si>
+    <t>Gated: No expired bill present in the current data set to edit — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>Detailed Bill Editing — Added Items Persist (DBE-06, EMI-6030)</t>
+  </si>
+  <si>
+    <t>DBE-06: items added while editing a Detailed Bill are saved and the total is recalculated</t>
+  </si>
+  <si>
+    <t>Skipped: No bills present in the current data set to edit — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>DBE-06b: a 200 OK on the update is not treated as proof the edit saved</t>
+  </si>
+  <si>
+    <t>Gated: No bills present in the current data set to edit — verify UAT data setup.</t>
+  </si>
+  <si>
+    <t>BusinessTestCases/BillManagement/ui/BillItems.spec.ts</t>
+  </si>
+  <si>
+    <t>Bill Items UI — Item Info Step Controls (BI-U01, BI-U02)</t>
+  </si>
+  <si>
+    <t>BI-U01: each item row in the Item Info step should expose edit and delete icons (EMI-3631)</t>
+  </si>
+  <si>
+    <t>BI-U02: the Item Info step should show a Back button to return to the previous step (EMI-3631)</t>
+  </si>
+  <si>
+    <t>Bill Items UI — Item Table Scrolling (BI-U03)</t>
+  </si>
+  <si>
+    <t>BI-U03: the item tables in the Add Items and Item Info steps should scroll vertically (EMI-3630)</t>
+  </si>
+  <si>
+    <t>Bill Items UI — Discount Amount Display (BI-U04)</t>
+  </si>
+  <si>
+    <t>BI-U04: Discount Amount should be visible in both the bill summary and the item details view (EMI-3270)</t>
+  </si>
+  <si>
+    <t>Skipped: No existing detailed bill available to view — verify UAT data setup.</t>
+  </si>
+  <si>
     <t>Summary — BillManagement</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.241Z</t>
+    <t>2026-09-08T15:08:53.323Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>functional</t>
   </si>
   <si>
+    <t>ui</t>
+  </si>
+  <si>
     <t>Count by status</t>
   </si>
   <si>
@@ -140,7 +398,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -158,6 +419,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -167,7 +429,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,11 +439,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,8 +456,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -542,18 +803,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,36 +846,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -637,39 +901,39 @@
         <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -680,13 +944,13 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -695,39 +959,39 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -738,13 +1002,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -756,36 +1020,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -814,124 +1078,1458 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="G13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>12</v>
+      <c r="B33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -939,84 +2537,139 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>118</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="B4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="B7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="4">
-        <v>1</v>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
